--- a/data/trans_orig/P70C1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P70C1_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si vuelven demasiado cansados a casa como para hacer las tareas domésticas necesarias en 2023</t>
+          <t>Población según si vuelven demasiado cansados a casa como para hacer las tareas domésticas necesarias en 2023 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26185</t>
+          <t>26046</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48701</t>
+          <t>49840</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15156</t>
+          <t>15513</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30495</t>
+          <t>31222</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47575</t>
+          <t>46526</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75464</t>
+          <t>73343</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>34,51%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20501</t>
+          <t>20548</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42898</t>
+          <t>46122</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3488</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12770</t>
+          <t>13426</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26709</t>
+          <t>27582</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52839</t>
+          <t>53189</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7704</t>
+          <t>7888</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23596</t>
+          <t>23348</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19109</t>
+          <t>17707</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16395</t>
+          <t>16049</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35712</t>
+          <t>34576</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15521</t>
+          <t>16490</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35199</t>
+          <t>35868</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>7485</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18871</t>
+          <t>18856</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27116</t>
+          <t>26243</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49800</t>
+          <t>47491</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8002</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21816</t>
+          <t>22113</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10636</t>
+          <t>10375</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23599</t>
+          <t>22846</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22093</t>
+          <t>21820</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39657</t>
+          <t>40233</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6639</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20394</t>
+          <t>19981</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26971</t>
+          <t>28625</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>14752</t>
+          <t>15748</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>39941</t>
+          <t>43624</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>386044</t>
+          <t>381459</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>926822</t>
+          <t>953176</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>217752</t>
+          <t>216549</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455925</t>
+          <t>441091</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>653493</t>
+          <t>656550</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1363197</t>
+          <t>1348887</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,01%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>106040</t>
+          <t>105075</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>257654</t>
+          <t>257027</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>121340</t>
+          <t>124698</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182971</t>
+          <t>187428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>261928</t>
+          <t>251490</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>420155</t>
+          <t>421208</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,12%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72354</t>
+          <t>69238</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>173106</t>
+          <t>174315</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81077</t>
+          <t>78919</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128106</t>
+          <t>126830</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>164931</t>
+          <t>167631</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>282719</t>
+          <t>283902</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>114812</t>
+          <t>115653</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>264425</t>
+          <t>265656</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>112251</t>
+          <t>108458</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170188</t>
+          <t>167854</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>245044</t>
+          <t>239751</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>413382</t>
+          <t>408981</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100801</t>
+          <t>98009</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>250014</t>
+          <t>246557</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>109157</t>
+          <t>110786</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>172308</t>
+          <t>170380</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>239055</t>
+          <t>230206</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>397593</t>
+          <t>398941</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36900</t>
+          <t>35554</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>94287</t>
+          <t>95104</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75151</t>
+          <t>72039</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>117108</t>
+          <t>117727</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120298</t>
+          <t>117157</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>200929</t>
+          <t>202404</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>167386</t>
+          <t>166965</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>214159</t>
+          <t>212759</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>143495</t>
+          <t>141371</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>180628</t>
+          <t>177364</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>322768</t>
+          <t>323530</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>380465</t>
+          <t>380934</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,92%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>79302</t>
+          <t>76433</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>125180</t>
+          <t>123696</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73798</t>
+          <t>72727</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>102133</t>
+          <t>98713</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>158389</t>
+          <t>160405</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>211254</t>
+          <t>213686</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32602</t>
+          <t>32259</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57863</t>
+          <t>60083</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29720</t>
+          <t>29713</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49391</t>
+          <t>49254</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>68897</t>
+          <t>67874</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>99274</t>
+          <t>99448</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52500</t>
+          <t>53770</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>87805</t>
+          <t>89338</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49567</t>
+          <t>50552</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>75322</t>
+          <t>75628</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>109198</t>
+          <t>110115</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>151409</t>
+          <t>152287</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19258</t>
+          <t>19289</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45081</t>
+          <t>44886</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52057</t>
+          <t>52933</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80354</t>
+          <t>79743</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>77279</t>
+          <t>76456</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>113869</t>
+          <t>115452</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11458</t>
+          <t>11717</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32266</t>
+          <t>31197</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18675</t>
+          <t>19037</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>35339</t>
+          <t>36555</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>34564</t>
+          <t>34910</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>61188</t>
+          <t>60866</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>617314</t>
+          <t>615859</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1191332</t>
+          <t>1220442</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>407757</t>
+          <t>407121</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>632869</t>
+          <t>630862</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1070899</t>
+          <t>1060185</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1795696</t>
+          <t>1756657</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>51,29%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>212110</t>
+          <t>208974</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>388069</t>
+          <t>392574</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>211093</t>
+          <t>212211</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>282718</t>
+          <t>281375</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>442240</t>
+          <t>449341</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>647321</t>
+          <t>654012</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>133756</t>
+          <t>126448</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>235129</t>
+          <t>233398</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>128384</t>
+          <t>122924</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>179508</t>
+          <t>174707</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>261207</t>
+          <t>267204</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>393502</t>
+          <t>391660</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>207375</t>
+          <t>192876</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>356552</t>
+          <t>358464</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>178336</t>
+          <t>178589</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>245491</t>
+          <t>244016</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>400760</t>
+          <t>407241</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>580366</t>
+          <t>586966</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>151379</t>
+          <t>156187</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>284943</t>
+          <t>285574</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>189797</t>
+          <t>190121</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>256653</t>
+          <t>253839</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>350230</t>
+          <t>366650</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>521893</t>
+          <t>528451</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>67994</t>
+          <t>64684</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>130162</t>
+          <t>129435</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>109579</t>
+          <t>111153</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>160212</t>
+          <t>160099</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>187741</t>
+          <t>187735</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>279055</t>
+          <t>274081</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70C1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P70C1_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>37223</t>
+          <t>52637</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26046</t>
+          <t>40298</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49840</t>
+          <t>67599</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22718</t>
+          <t>25941</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15513</t>
+          <t>18694</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31222</t>
+          <t>34240</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>59941</t>
+          <t>78578</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46526</t>
+          <t>62774</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73343</t>
+          <t>94476</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>37,73%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29775</t>
+          <t>34395</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20548</t>
+          <t>23327</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46122</t>
+          <t>48334</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13426</t>
+          <t>13142</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>36920</t>
+          <t>41984</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27582</t>
+          <t>30708</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53189</t>
+          <t>55615</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14399</t>
+          <t>15002</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7888</t>
+          <t>7537</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23348</t>
+          <t>24328</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>11148</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>6211</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17707</t>
+          <t>18907</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>23855</t>
+          <t>26150</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16049</t>
+          <t>17768</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34576</t>
+          <t>37721</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24400</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16490</t>
+          <t>17630</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35868</t>
+          <t>38639</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12406</t>
+          <t>15723</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>10443</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>22569</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>36805</t>
+          <t>42806</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26243</t>
+          <t>31277</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47491</t>
+          <t>56814</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13796</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>10950</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22113</t>
+          <t>28180</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16635</t>
+          <t>19664</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10375</t>
+          <t>13470</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22846</t>
+          <t>27145</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>30431</t>
+          <t>38710</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21820</t>
+          <t>28478</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40233</t>
+          <t>51198</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12344</t>
+          <t>13658</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6639</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19981</t>
+          <t>22423</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12250</t>
+          <t>8535</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28625</t>
+          <t>14362</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>24594</t>
+          <t>22193</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15748</t>
+          <t>14878</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>43624</t>
+          <t>33569</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>131937</t>
+          <t>161821</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>131937</t>
+          <t>161821</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131937</t>
+          <t>161821</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>80609</t>
+          <t>88600</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80609</t>
+          <t>88600</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80609</t>
+          <t>88600</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>212546</t>
+          <t>250421</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>212546</t>
+          <t>250421</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>212546</t>
+          <t>250421</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>568634</t>
+          <t>355431</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>381459</t>
+          <t>319931</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>953176</t>
+          <t>390477</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>295410</t>
+          <t>216691</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>216549</t>
+          <t>193812</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>441091</t>
+          <t>243358</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>864044</t>
+          <t>572122</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>656550</t>
+          <t>531519</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1348887</t>
+          <t>615469</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>202411</t>
+          <t>228609</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>105075</t>
+          <t>198951</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>257027</t>
+          <t>261520</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>157378</t>
+          <t>181731</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>124698</t>
+          <t>158682</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>187428</t>
+          <t>204384</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>359789</t>
+          <t>410340</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>251490</t>
+          <t>371296</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>421208</t>
+          <t>445170</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>135534</t>
+          <t>159859</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69238</t>
+          <t>135671</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>174315</t>
+          <t>187467</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>106025</t>
+          <t>119013</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78919</t>
+          <t>102388</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126830</t>
+          <t>140698</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>241559</t>
+          <t>278871</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>167631</t>
+          <t>251485</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>283902</t>
+          <t>313572</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>208539</t>
+          <t>233455</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>115653</t>
+          <t>204004</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>265656</t>
+          <t>266776</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>142868</t>
+          <t>157693</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>108458</t>
+          <t>137489</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>167854</t>
+          <t>181416</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>351408</t>
+          <t>391148</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>239751</t>
+          <t>356554</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>408981</t>
+          <t>431079</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>195653</t>
+          <t>211651</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>98009</t>
+          <t>183083</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>246557</t>
+          <t>242964</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>144524</t>
+          <t>161194</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>110786</t>
+          <t>141938</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>170380</t>
+          <t>182852</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>340177</t>
+          <t>372845</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>230206</t>
+          <t>337579</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>398941</t>
+          <t>413816</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>70686</t>
+          <t>82346</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35554</t>
+          <t>65097</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>95104</t>
+          <t>106013</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>6,48%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>5,12%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>97524</t>
+          <t>108266</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72039</t>
+          <t>91703</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>117727</t>
+          <t>124762</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>168210</t>
+          <t>190611</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117157</t>
+          <t>165793</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>202404</t>
+          <t>217961</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1381457</t>
+          <t>1271351</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1381457</t>
+          <t>1271351</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1381457</t>
+          <t>1271351</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>943730</t>
+          <t>944587</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>943730</t>
+          <t>944587</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>943730</t>
+          <t>944587</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2325188</t>
+          <t>2215938</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2325188</t>
+          <t>2215938</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2325188</t>
+          <t>2215938</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>190226</t>
+          <t>204936</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>166965</t>
+          <t>183647</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>212759</t>
+          <t>230790</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>160262</t>
+          <t>170612</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>141371</t>
+          <t>152753</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>177364</t>
+          <t>190369</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>350489</t>
+          <t>375548</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>323530</t>
+          <t>346389</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>380934</t>
+          <t>405457</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>41,77%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>96880</t>
+          <t>100461</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>76433</t>
+          <t>82063</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123696</t>
+          <t>121478</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>86045</t>
+          <t>93880</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72727</t>
+          <t>80015</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>98713</t>
+          <t>110607</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>182925</t>
+          <t>194342</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>160405</t>
+          <t>171674</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>213686</t>
+          <t>220952</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>44175</t>
+          <t>50010</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32259</t>
+          <t>38013</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60083</t>
+          <t>64581</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>38469</t>
+          <t>45363</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29713</t>
+          <t>35561</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49254</t>
+          <t>58067</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>82644</t>
+          <t>95374</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>67874</t>
+          <t>78127</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>99448</t>
+          <t>113160</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>68857</t>
+          <t>76984</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>53770</t>
+          <t>59586</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>89338</t>
+          <t>102348</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>61795</t>
+          <t>69466</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>50552</t>
+          <t>56967</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>75628</t>
+          <t>84798</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>130653</t>
+          <t>146450</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>110115</t>
+          <t>123847</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>152287</t>
+          <t>170326</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>29368</t>
+          <t>34242</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19289</t>
+          <t>22550</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44886</t>
+          <t>49595</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>65236</t>
+          <t>72112</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52933</t>
+          <t>59557</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>79743</t>
+          <t>87609</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>94604</t>
+          <t>106354</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>76456</t>
+          <t>87796</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>115452</t>
+          <t>126557</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>20119</t>
+          <t>24024</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11717</t>
+          <t>14176</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31197</t>
+          <t>36826</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>26030</t>
+          <t>28513</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19037</t>
+          <t>20828</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>36555</t>
+          <t>38536</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>46150</t>
+          <t>52537</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>34910</t>
+          <t>38882</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>60866</t>
+          <t>68262</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>449625</t>
+          <t>490659</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>449625</t>
+          <t>490659</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>449625</t>
+          <t>490659</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>437839</t>
+          <t>479946</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>437839</t>
+          <t>479946</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>437839</t>
+          <t>479946</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>887464</t>
+          <t>970605</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>887464</t>
+          <t>970605</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>887464</t>
+          <t>970605</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>796083</t>
+          <t>613004</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>615859</t>
+          <t>567524</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1220442</t>
+          <t>654750</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>478391</t>
+          <t>413244</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>407121</t>
+          <t>382341</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>630862</t>
+          <t>448650</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1274474</t>
+          <t>1026248</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1060185</t>
+          <t>970353</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1756657</t>
+          <t>1085947</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>329066</t>
+          <t>363465</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>208974</t>
+          <t>329748</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>392574</t>
+          <t>402929</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>250568</t>
+          <t>283200</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>212211</t>
+          <t>258074</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>281375</t>
+          <t>311175</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>579634</t>
+          <t>646666</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>449341</t>
+          <t>602036</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>654012</t>
+          <t>697200</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>194108</t>
+          <t>224870</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>126448</t>
+          <t>198129</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>233398</t>
+          <t>259317</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>153950</t>
+          <t>175524</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>122924</t>
+          <t>154903</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>174707</t>
+          <t>198497</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>348058</t>
+          <t>400395</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>267204</t>
+          <t>363881</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>391660</t>
+          <t>439965</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>301796</t>
+          <t>337522</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>192876</t>
+          <t>301194</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>358464</t>
+          <t>380680</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>217070</t>
+          <t>242882</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>178589</t>
+          <t>218970</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>244016</t>
+          <t>271064</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>518866</t>
+          <t>580404</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>407241</t>
+          <t>537604</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>586966</t>
+          <t>627120</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>238817</t>
+          <t>264940</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>156187</t>
+          <t>229063</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>285574</t>
+          <t>300889</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>226395</t>
+          <t>252970</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>190121</t>
+          <t>226859</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>253839</t>
+          <t>277952</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>465212</t>
+          <t>517910</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>366650</t>
+          <t>470707</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>528451</t>
+          <t>560731</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>103150</t>
+          <t>120028</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>64684</t>
+          <t>98572</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>129435</t>
+          <t>146962</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>135805</t>
+          <t>145314</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>111153</t>
+          <t>126975</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>160099</t>
+          <t>165894</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>238954</t>
+          <t>265342</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>187735</t>
+          <t>232701</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>274081</t>
+          <t>294490</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1963020</t>
+          <t>1923830</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1963020</t>
+          <t>1923830</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1963020</t>
+          <t>1923830</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1462179</t>
+          <t>1513133</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1462179</t>
+          <t>1513133</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1462179</t>
+          <t>1513133</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>3425198</t>
+          <t>3436963</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3425198</t>
+          <t>3436963</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3425198</t>
+          <t>3436963</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
